--- a/public/inputs/y07-portuguese-2nd - input.xlsx
+++ b/public/inputs/y07-portuguese-2nd - input.xlsx
@@ -441,10 +441,9 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Unidade 1 · Cumprimentose Identificação</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr"/>
+          <t>Unidade 1 · Cumprimentos e Identificação</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -457,7 +456,6 @@
           <t>Unidade 2 · Dados Pessoais</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -467,10 +465,9 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Unidade 3 · Famíliae Alimentação</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr"/>
+          <t>Unidade 3 · Família e Alimentação</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -483,7 +480,6 @@
           <t>Unidade 4 · Habitação</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -493,10 +489,9 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Unidade 5 · Espaços Comerciaise Serviços</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr"/>
+          <t>Unidade 5 · Espaços Comerciais e Serviços</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -506,10 +501,9 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Unidade 6 · Saúdee Actividade Física</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr"/>
+          <t>Unidade 6 · Saúde e Actividade Física</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -522,7 +516,6 @@
           <t>Unidade 6 · Exercícios de revisão</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -532,10 +525,9 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Unidade 7 · Tempos Livrese Convívio Social</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr"/>
+          <t>Unidade 7 · Tempos Livres e Convívio Social</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -548,7 +540,6 @@
           <t>Unidade 7 · Exercícios de revisão</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -561,7 +552,6 @@
           <t>Unidade 8 · Informação Pessoal</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -574,7 +564,6 @@
           <t>Unidade 9 · Rotina Diária</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -587,7 +576,6 @@
           <t>Unidade 9 · Exercícios de revisão</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -597,10 +585,9 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Unidade 10 · Famíliae Compreensão Social</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr"/>
+          <t>Unidade 10 · Família e Compreensão Social</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -613,7 +600,6 @@
           <t>Unidade 10 · Exercícios de revisão</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -623,10 +609,9 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Unidade 11 · Alimentaçãoe Dieta</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr"/>
+          <t>Unidade 11 · Alimentação e Dieta</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -639,7 +624,6 @@
           <t>Unidade 11 · Exercícios de revisão</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
